--- a/docs/tampermonkey/发票模板/云冠清关发票模板.xlsx
+++ b/docs/tampermonkey/发票模板/云冠清关发票模板.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\代码\hth123321\docs\tampermonkey\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\代码\hth123321\docs\tampermonkey\发票模板\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{301F2C6B-627C-420E-9560-38B6153E1275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B591810C-A0EA-4F26-8111-D7416055A071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="74">
   <si>
     <t>发票</t>
   </si>
@@ -960,6 +960,10 @@
   </si>
   <si>
     <t>{{shipment.address.addressLine1}}</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{t.brand}}</t>
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
 </sst>
@@ -1367,6 +1371,36 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="3" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="3" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1385,9 +1419,6 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1396,33 +1427,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="3" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="10" fillId="3" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1822,70 +1826,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="35"/>
-      <c r="R1" s="35"/>
-      <c r="S1" s="35"/>
-      <c r="T1" s="35"/>
-      <c r="U1" s="35"/>
-      <c r="V1" s="35"/>
-      <c r="W1" s="35"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
+      <c r="K1" s="45"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="45"/>
+      <c r="N1" s="45"/>
+      <c r="O1" s="45"/>
+      <c r="P1" s="45"/>
+      <c r="Q1" s="45"/>
+      <c r="R1" s="45"/>
+      <c r="S1" s="45"/>
+      <c r="T1" s="45"/>
+      <c r="U1" s="45"/>
+      <c r="V1" s="45"/>
+      <c r="W1" s="45"/>
     </row>
     <row r="2" spans="1:26" s="1" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="36" t="s">
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
-      <c r="L2" s="37"/>
-      <c r="M2" s="37"/>
-      <c r="N2" s="37"/>
-      <c r="O2" s="37"/>
-      <c r="P2" s="37"/>
-      <c r="Q2" s="37"/>
-      <c r="R2" s="37"/>
-      <c r="S2" s="37"/>
-      <c r="T2" s="37"/>
-      <c r="U2" s="37"/>
-      <c r="V2" s="37"/>
-      <c r="W2" s="37"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
+      <c r="K2" s="47"/>
+      <c r="L2" s="47"/>
+      <c r="M2" s="47"/>
+      <c r="N2" s="47"/>
+      <c r="O2" s="47"/>
+      <c r="P2" s="47"/>
+      <c r="Q2" s="47"/>
+      <c r="R2" s="47"/>
+      <c r="S2" s="47"/>
+      <c r="T2" s="47"/>
+      <c r="U2" s="47"/>
+      <c r="V2" s="47"/>
+      <c r="W2" s="47"/>
     </row>
     <row r="3" spans="1:26" s="1" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="48" t="s">
         <v>65</v>
       </c>
-      <c r="C3" s="39"/>
-      <c r="D3" s="40"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="50"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="2"/>
@@ -1910,9 +1914,9 @@
       <c r="A4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
       <c r="E4" s="7" t="s">
         <v>5</v>
       </c>
@@ -1922,127 +1926,127 @@
       <c r="G4" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="42" t="s">
+      <c r="H4" s="51" t="s">
         <v>70</v>
       </c>
-      <c r="I4" s="43"/>
-      <c r="J4" s="43"/>
-      <c r="K4" s="43"/>
-      <c r="L4" s="43"/>
-      <c r="M4" s="43"/>
-      <c r="N4" s="43"/>
-      <c r="O4" s="43"/>
-      <c r="P4" s="43"/>
-      <c r="Q4" s="43"/>
-      <c r="R4" s="43"/>
-      <c r="S4" s="43"/>
-      <c r="T4" s="43"/>
-      <c r="U4" s="43"/>
-      <c r="V4" s="43"/>
-      <c r="W4" s="44"/>
+      <c r="I4" s="52"/>
+      <c r="J4" s="52"/>
+      <c r="K4" s="52"/>
+      <c r="L4" s="52"/>
+      <c r="M4" s="52"/>
+      <c r="N4" s="52"/>
+      <c r="O4" s="52"/>
+      <c r="P4" s="52"/>
+      <c r="Q4" s="52"/>
+      <c r="R4" s="52"/>
+      <c r="S4" s="52"/>
+      <c r="T4" s="52"/>
+      <c r="U4" s="52"/>
+      <c r="V4" s="52"/>
+      <c r="W4" s="53"/>
     </row>
     <row r="5" spans="1:26" s="1" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="41"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
+      <c r="B5" s="44"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
       <c r="G5" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="45"/>
-      <c r="K5" s="45"/>
-      <c r="L5" s="45"/>
-      <c r="M5" s="45"/>
-      <c r="N5" s="45"/>
-      <c r="O5" s="45"/>
-      <c r="P5" s="45"/>
-      <c r="Q5" s="45"/>
-      <c r="R5" s="45"/>
-      <c r="S5" s="45"/>
-      <c r="T5" s="45"/>
-      <c r="U5" s="45"/>
-      <c r="V5" s="45"/>
-      <c r="W5" s="45"/>
+      <c r="H5" s="36"/>
+      <c r="I5" s="36"/>
+      <c r="J5" s="36"/>
+      <c r="K5" s="36"/>
+      <c r="L5" s="36"/>
+      <c r="M5" s="36"/>
+      <c r="N5" s="36"/>
+      <c r="O5" s="36"/>
+      <c r="P5" s="36"/>
+      <c r="Q5" s="36"/>
+      <c r="R5" s="36"/>
+      <c r="S5" s="36"/>
+      <c r="T5" s="36"/>
+      <c r="U5" s="36"/>
+      <c r="V5" s="36"/>
+      <c r="W5" s="36"/>
     </row>
     <row r="6" spans="1:26" s="1" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="46"/>
-      <c r="C6" s="46"/>
-      <c r="D6" s="46"/>
-      <c r="E6" s="46"/>
-      <c r="F6" s="46"/>
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
       <c r="G6" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="H6" s="45" t="s">
+      <c r="H6" s="36" t="s">
         <v>71</v>
       </c>
-      <c r="I6" s="45"/>
-      <c r="J6" s="45"/>
-      <c r="K6" s="45"/>
-      <c r="L6" s="45"/>
-      <c r="M6" s="45"/>
+      <c r="I6" s="36"/>
+      <c r="J6" s="36"/>
+      <c r="K6" s="36"/>
+      <c r="L6" s="36"/>
+      <c r="M6" s="36"/>
       <c r="N6" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="O6" s="45" t="s">
+      <c r="O6" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="P6" s="45"/>
-      <c r="Q6" s="45"/>
-      <c r="R6" s="45"/>
-      <c r="S6" s="45"/>
-      <c r="T6" s="45"/>
-      <c r="U6" s="45"/>
-      <c r="V6" s="45"/>
-      <c r="W6" s="45"/>
+      <c r="P6" s="36"/>
+      <c r="Q6" s="36"/>
+      <c r="R6" s="36"/>
+      <c r="S6" s="36"/>
+      <c r="T6" s="36"/>
+      <c r="U6" s="36"/>
+      <c r="V6" s="36"/>
+      <c r="W6" s="36"/>
     </row>
     <row r="7" spans="1:26" s="1" customFormat="1" ht="41.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="46"/>
-      <c r="C7" s="46"/>
-      <c r="D7" s="46"/>
-      <c r="E7" s="46"/>
-      <c r="F7" s="46"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
       <c r="G7" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="45" t="s">
+      <c r="H7" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="I7" s="45"/>
-      <c r="J7" s="45"/>
-      <c r="K7" s="45"/>
-      <c r="L7" s="45"/>
-      <c r="M7" s="45"/>
-      <c r="N7" s="45"/>
-      <c r="O7" s="45"/>
-      <c r="P7" s="45"/>
-      <c r="Q7" s="45"/>
-      <c r="R7" s="45"/>
-      <c r="S7" s="45"/>
-      <c r="T7" s="45"/>
-      <c r="U7" s="45"/>
-      <c r="V7" s="45"/>
-      <c r="W7" s="45"/>
+      <c r="I7" s="36"/>
+      <c r="J7" s="36"/>
+      <c r="K7" s="36"/>
+      <c r="L7" s="36"/>
+      <c r="M7" s="36"/>
+      <c r="N7" s="36"/>
+      <c r="O7" s="36"/>
+      <c r="P7" s="36"/>
+      <c r="Q7" s="36"/>
+      <c r="R7" s="36"/>
+      <c r="S7" s="36"/>
+      <c r="T7" s="36"/>
+      <c r="U7" s="36"/>
+      <c r="V7" s="36"/>
+      <c r="W7" s="36"/>
     </row>
     <row r="8" spans="1:26" s="1" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="47"/>
-      <c r="C8" s="46"/>
-      <c r="D8" s="46"/>
+      <c r="B8" s="42"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
       <c r="E8" s="6" t="s">
         <v>14</v>
       </c>
@@ -2050,36 +2054,36 @@
       <c r="G8" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="H8" s="45" t="s">
+      <c r="H8" s="36" t="s">
         <v>67</v>
       </c>
-      <c r="I8" s="45"/>
-      <c r="J8" s="45"/>
-      <c r="K8" s="45"/>
-      <c r="L8" s="45"/>
-      <c r="M8" s="45"/>
+      <c r="I8" s="36"/>
+      <c r="J8" s="36"/>
+      <c r="K8" s="36"/>
+      <c r="L8" s="36"/>
+      <c r="M8" s="36"/>
       <c r="N8" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="O8" s="48" t="s">
+      <c r="O8" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="P8" s="48"/>
-      <c r="Q8" s="48"/>
-      <c r="R8" s="48"/>
-      <c r="S8" s="48"/>
-      <c r="T8" s="48"/>
-      <c r="U8" s="48"/>
-      <c r="V8" s="48"/>
-      <c r="W8" s="48"/>
+      <c r="P8" s="43"/>
+      <c r="Q8" s="43"/>
+      <c r="R8" s="43"/>
+      <c r="S8" s="43"/>
+      <c r="T8" s="43"/>
+      <c r="U8" s="43"/>
+      <c r="V8" s="43"/>
+      <c r="W8" s="43"/>
     </row>
     <row r="9" spans="1:26" s="1" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="45"/>
-      <c r="C9" s="45"/>
-      <c r="D9" s="45"/>
+      <c r="B9" s="36"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="36"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
@@ -2087,86 +2091,86 @@
       <c r="G9" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H9" s="50">
+      <c r="H9" s="37">
         <v>61406640022</v>
       </c>
-      <c r="I9" s="51"/>
-      <c r="J9" s="51"/>
-      <c r="K9" s="51"/>
-      <c r="L9" s="51"/>
-      <c r="M9" s="52"/>
+      <c r="I9" s="38"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="38"/>
+      <c r="L9" s="38"/>
+      <c r="M9" s="39"/>
       <c r="N9" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="O9" s="53" t="s">
+      <c r="O9" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="P9" s="53"/>
-      <c r="Q9" s="53"/>
-      <c r="R9" s="53"/>
-      <c r="S9" s="53"/>
-      <c r="T9" s="53"/>
-      <c r="U9" s="53"/>
-      <c r="V9" s="53"/>
-      <c r="W9" s="53"/>
+      <c r="P9" s="40"/>
+      <c r="Q9" s="40"/>
+      <c r="R9" s="40"/>
+      <c r="S9" s="40"/>
+      <c r="T9" s="40"/>
+      <c r="U9" s="40"/>
+      <c r="V9" s="40"/>
+      <c r="W9" s="40"/>
     </row>
     <row r="10" spans="1:26" s="1" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="49"/>
-      <c r="C10" s="45"/>
-      <c r="D10" s="45"/>
-      <c r="E10" s="45"/>
-      <c r="F10" s="45"/>
+      <c r="B10" s="35"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="36"/>
       <c r="G10" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="H10" s="45"/>
-      <c r="I10" s="45"/>
-      <c r="J10" s="45"/>
-      <c r="K10" s="45"/>
-      <c r="L10" s="45"/>
-      <c r="M10" s="45"/>
-      <c r="N10" s="45"/>
-      <c r="O10" s="45"/>
-      <c r="P10" s="45"/>
-      <c r="Q10" s="45"/>
-      <c r="R10" s="45"/>
-      <c r="S10" s="45"/>
-      <c r="T10" s="45"/>
-      <c r="U10" s="45"/>
-      <c r="V10" s="45"/>
-      <c r="W10" s="45"/>
+      <c r="H10" s="36"/>
+      <c r="I10" s="36"/>
+      <c r="J10" s="36"/>
+      <c r="K10" s="36"/>
+      <c r="L10" s="36"/>
+      <c r="M10" s="36"/>
+      <c r="N10" s="36"/>
+      <c r="O10" s="36"/>
+      <c r="P10" s="36"/>
+      <c r="Q10" s="36"/>
+      <c r="R10" s="36"/>
+      <c r="S10" s="36"/>
+      <c r="T10" s="36"/>
+      <c r="U10" s="36"/>
+      <c r="V10" s="36"/>
+      <c r="W10" s="36"/>
     </row>
     <row r="11" spans="1:26" s="1" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="49" t="s">
+      <c r="B11" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="45"/>
-      <c r="D11" s="45"/>
-      <c r="E11" s="45"/>
-      <c r="F11" s="45"/>
-      <c r="G11" s="45"/>
-      <c r="H11" s="45"/>
-      <c r="I11" s="45"/>
-      <c r="J11" s="45"/>
-      <c r="K11" s="45"/>
-      <c r="L11" s="45"/>
-      <c r="M11" s="45"/>
-      <c r="N11" s="45"/>
-      <c r="O11" s="45"/>
-      <c r="P11" s="45"/>
-      <c r="Q11" s="45"/>
-      <c r="R11" s="45"/>
-      <c r="S11" s="45"/>
-      <c r="T11" s="45"/>
-      <c r="U11" s="45"/>
-      <c r="V11" s="45"/>
-      <c r="W11" s="45"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="36"/>
+      <c r="F11" s="36"/>
+      <c r="G11" s="36"/>
+      <c r="H11" s="36"/>
+      <c r="I11" s="36"/>
+      <c r="J11" s="36"/>
+      <c r="K11" s="36"/>
+      <c r="L11" s="36"/>
+      <c r="M11" s="36"/>
+      <c r="N11" s="36"/>
+      <c r="O11" s="36"/>
+      <c r="P11" s="36"/>
+      <c r="Q11" s="36"/>
+      <c r="R11" s="36"/>
+      <c r="S11" s="36"/>
+      <c r="T11" s="36"/>
+      <c r="U11" s="36"/>
+      <c r="V11" s="36"/>
+      <c r="W11" s="36"/>
     </row>
     <row r="12" spans="1:26" ht="66" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="13" t="s">
@@ -2319,7 +2323,9 @@
         <v>59</v>
       </c>
       <c r="R14" s="16"/>
-      <c r="S14" s="19"/>
+      <c r="S14" s="19" t="s">
+        <v>73</v>
+      </c>
       <c r="T14" s="26"/>
       <c r="U14" s="26"/>
       <c r="V14" s="26"/>
@@ -2554,28 +2560,28 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A1:W1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="G2:W2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="H4:W4"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="H5:W5"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="H6:M6"/>
+    <mergeCell ref="O6:W6"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="H7:W7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="O8:W8"/>
     <mergeCell ref="B11:W11"/>
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="H9:M9"/>
     <mergeCell ref="O9:W9"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="H10:W10"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="H7:W7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="H8:M8"/>
-    <mergeCell ref="O8:W8"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="H5:W5"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="H6:M6"/>
-    <mergeCell ref="O6:W6"/>
-    <mergeCell ref="A1:W1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="G2:W2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="H4:W4"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <hyperlinks>
